--- a/output/pdf_financials_xlsx/ECOM.xlsx
+++ b/output/pdf_financials_xlsx/ECOM.xlsx
@@ -2817,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.020943</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.273839</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.06379899999999999</v>
       </c>
     </row>
     <row r="92">
@@ -2842,13 +2842,13 @@
         <v>0.101368</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.039566</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.977569</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.571097</v>
       </c>
     </row>
     <row r="93">
@@ -5156,7 +5156,11 @@
           <t>Reserves 15, 16</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -5198,7 +5202,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ECOM.xlsx
+++ b/output/pdf_financials_xlsx/ECOM.xlsx
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.132592</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.051312</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.132592</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.051312</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.767297</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.881574</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.537658</v>
       </c>
     </row>
     <row r="35">
@@ -1392,13 +1392,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.767297</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.881574</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.537658</v>
       </c>
     </row>
     <row r="37">
@@ -1692,13 +1692,13 @@
         <v>0.542748</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.775475</v>
+        <v>2.008178</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.21614</v>
+        <v>1.334566</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.145997</v>
+        <v>0.608339</v>
       </c>
     </row>
     <row r="49">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">

--- a/output/pdf_financials_xlsx/ECOM.xlsx
+++ b/output/pdf_financials_xlsx/ECOM.xlsx
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-17.382835</v>
+        <v>-16.078827</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-21.256884</v>
+        <v>-18.99519</v>
       </c>
     </row>
     <row r="17">
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.304008</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.261694</v>
       </c>
     </row>
     <row r="18">
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-2.918949</v>
+        <v>-14.463886</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.440536</v>
+        <v>-21.69742</v>
       </c>
     </row>
     <row r="21">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-2.918949</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>0.440536</v>
       </c>
     </row>
     <row r="22">
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-17.382835</v>
+        <v>-16.078827</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-21.256884</v>
+        <v>-18.99519</v>
       </c>
     </row>
     <row r="28">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-12.645846</v>
+        <v>-11.341838</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-17.19152</v>
+        <v>-14.929826</v>
       </c>
     </row>
     <row r="30">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-39.89369837195387</v>
+        <v>-35.77996000865141</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-72.14519651365137</v>
+        <v>-62.65386834233516</v>
       </c>
     </row>
     <row r="31">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-8.110094100769913</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.90666689830426</v>
       </c>
     </row>
     <row r="32">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.231295</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>1.928245</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.003242</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.457128</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.106562</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.175133</v>
       </c>
     </row>
     <row r="41">
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.234537</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.928245</v>
+        <v>2.385373</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.95505</v>
+        <v>3.061612</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.429807</v>
+        <v>1.60494</v>
       </c>
     </row>
     <row r="42">
@@ -1689,16 +1689,16 @@
         <v>0.6026860000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.542748</v>
+        <v>0.308211</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.008178</v>
+        <v>1.55105</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.334566</v>
+        <v>1.228004</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.608339</v>
+        <v>0.433206</v>
       </c>
     </row>
     <row r="49">
@@ -10042,7 +10042,11 @@
           <t>Income tax recovery 26</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10086,7 +10090,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -10132,7 +10140,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
